--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0054.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0054.xlsx
@@ -1616,7 +1616,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Okay.</t>
+          <t>Ừ.</t>
         </is>
       </c>
     </row>
@@ -3182,7 +3182,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Ôi, cảm ơn {Male=cậu;Female=cô}! Giờ ngôi sao đã đến rồi, chắc chắn tôi sẽ khỏe lại thôi!</t>
+          <t>Ôi, cảm ơn bạn! Giờ ngôi sao đã đến rồi, chắc chắn tôi sẽ khỏe lại thôi!</t>
         </is>
       </c>
     </row>
@@ -7992,7 +7992,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Ta thấy chuyện này chẳng quan trọng gì cả!</t>
+          <t>Tao thấy chuyện này chẳng quan trọng gì cả!</t>
         </is>
       </c>
     </row>
@@ -8447,7 +8447,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Ta muốn ở bên mọi người và thấy Ragunna trở thành ngôi nhà như trong ký ức của ta.</t>
+          <t>Tao muốn ở bên mọi người và thấy Ragunna trở thành ngôi nhà như trong ký ức của tao.</t>
         </is>
       </c>
     </row>
@@ -9357,7 +9357,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Và... nếu cậu gặp khó khăn gì, đừng ngại mà gọi bọn ta nhé.</t>
+          <t>Và... nếu cậu gặp khó khăn gì, đừng ngại mà gọi bọn tao nhé.</t>
         </is>
       </c>
     </row>
@@ -10527,7 +10527,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Ta có mấy suất lương khẩn cấp đây. Cầm lấy đi.</t>
+          <t>Tao có mấy suất lương khẩn cấp đây. Cầm lấy đi.</t>
         </is>
       </c>
     </row>
@@ -14817,7 +14817,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Nó cứ làm những cử chỉ kỳ lạ và lẩm bẩm những lời ta không thể hiểu.</t>
+          <t>Nó cứ làm những cử chỉ kỳ lạ và lẩm bẩm những lời tao không thể hiểu.</t>
         </is>
       </c>
     </row>
@@ -15142,7 +15142,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Cậu nghĩ sao?</t>
+          <t>Mày nghĩ sao?</t>
         </is>
       </c>
     </row>
@@ -16702,7 +16702,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Ta nghĩ Imperator đã tách năng lượng dư thừa do Overclocking ra và giảm thiểu thương vong.</t>
+          <t>Tao nghĩ Imperator đã tách năng lượng dư thừa do Overclocking ra và giảm thiểu thương vong.</t>
         </is>
       </c>
     </row>
@@ -17677,7 +17677,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Ước gì ta có khả năng tiện lợi như thế.</t>
+          <t>Ước gì tao có khả năng tiện lợi như thế.</t>
         </is>
       </c>
     </row>
@@ -19432,7 +19432,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Thưa {Male=ngài;Female=nữ sĩ}, vừa trở về từ Avinoleum à?</t>
+          <t>Thưa {Male=Sir;Female=Madam}, vừa trở về từ Avinoleum à?</t>
         </is>
       </c>
     </row>
@@ -19627,7 +19627,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>…{Male=Thưa ngài;Female=Thưa quý bà}, có điều tôi phải hỏi, điều mà trước đây tôi chưa dám đặt ra.</t>
+          <t>…{Male=Sir;Female=Madam}, có điều tôi phải hỏi, điều mà trước đây tôi chưa dám đặt ra.</t>
         </is>
       </c>
     </row>
@@ -20797,7 +20797,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Ta hứa, ta sẽ hoàn thành cuốn hồi ký này và không để những kỷ vật quý giá này bị thời gian vùi lấp.</t>
+          <t>Tao hứa, tao sẽ hoàn thành cuốn hồi ký này và không để những kỷ vật quý giá này bị thời gian vùi lấp.</t>
         </is>
       </c>
     </row>
@@ -20862,7 +20862,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>...Cho đến khi ta gặp lại, {Male=thưa ngài;Female=thưa quý bà}.</t>
+          <t>...Cho đến khi ta gặp lại, {Male=sir;Female=madam}.</t>
         </is>
       </c>
     </row>
@@ -20992,7 +20992,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Ta hứa, ta sẽ hoàn thành cuốn hồi ký này và không để những kỷ vật quý giá này bị thời gian vùi lấp.</t>
+          <t>Tao hứa, tao sẽ hoàn thành cuốn hồi ký này và không để những kỷ vật quý giá này bị thời gian vùi lấp.</t>
         </is>
       </c>
     </row>
@@ -21122,7 +21122,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>...Cho đến khi ta gặp lại, {Male=thưa ngài;Female=thưa quý bà}.</t>
+          <t>...Cho đến khi ta gặp lại, {Male=sir;Female=madam}.</t>
         </is>
       </c>
     </row>
@@ -21642,7 +21642,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Xin lỗi {Male=ngài;Female=bà}, ngài có để ý thấy điều gì bất thường trên bầu trời kia không?</t>
+          <t>Xin lỗi {Male=sir;Female=madam}, ngài có để ý thấy điều gì bất thường trên bầu trời kia không?</t>
         </is>
       </c>
     </row>
@@ -22032,7 +22032,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Gì? Sao cậu...? À, ta cảm nhận được cậu là một Cộng Hưởng Giả mạnh mẽ. Không lý do gì cậu lại nói dối về chuyện đó.</t>
+          <t>Gì? Sao cậu...? À, tao cảm nhận được cậu là một Resonator mạnh mẽ. Không lý do gì cậu lại nói dối về chuyện đó.</t>
         </is>
       </c>
     </row>
@@ -23852,7 +23852,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Nhưng hãy nhớ điều này, ta sẽ quay lại bên ngươi bất cứ khi nào ngươi cần ta.</t>
+          <t>Nhưng hãy nhớ điều này, tao sẽ quay lại bên mày bất cứ khi nào mày cần tao.</t>
         </is>
       </c>
     </row>
@@ -25997,7 +25997,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Có chuyện gì vậy?</t>
+          <t>Sao rồi?</t>
         </is>
       </c>
     </row>
@@ -26322,7 +26322,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Ta không biết tụi cậu lại leo cao giỏi thế!</t>
+          <t>Tao không biết tụi cậu lại leo cao giỏi thế!</t>
         </is>
       </c>
     </row>
@@ -26907,7 +26907,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Để ta đi xem qua đã.</t>
+          <t>Để tao đi xem qua đã.</t>
         </is>
       </c>
     </row>
@@ -28012,7 +28012,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Hoan hô! {Male=Cậu ấy;Female=Cô ấy} đồng ý rồi! Ái, ái, ái! Ta biết tụi bay mừng, nhưng đừng có mà giật tóc ta chứ!</t>
+          <t>Hoan hô! {Male=He;Female=She} đồng ý rồi! Ái, ái, ái! Tao biết tụi bay mừng, nhưng đừng có mà giật tóc tao chứ!</t>
         </is>
       </c>
     </row>
@@ -28077,7 +28077,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Ồ, xin chào, {Male=anh;Female=chị} {PlayerName}!</t>
+          <t>Ồ, xin chào, {Male=Mr.;Female=Ms.} {PlayerName}!</t>
         </is>
       </c>
     </row>
@@ -28922,7 +28922,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Nào, mọi người bình tĩnh nào. Tôi đã bảo {Male=anh;Female=chị} {PlayerName} đang trên đường tới rồi mà... À, cậu đến rồi!</t>
+          <t>Nào, mọi người bình tĩnh nào. Tôi đã bảo {Male=Mr.;Female=Ms.} {PlayerName} đang trên đường tới rồi mà... À, cậu đến rồi!</t>
         </is>
       </c>
     </row>
@@ -29832,7 +29832,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>{Anh;Chị} {PlayerName} tìm thấy nó ở đâu thế? Có thể cho tôi xem mấy con Thú Nhồi Bông không? Nếu không phiền.</t>
+          <t>{Male=Mr.;Female=Ms.} {PlayerName} tìm thấy nó ở đâu thế? Có thể cho tôi xem mấy con Thú Nhồi Bông không? Nếu không phiền.</t>
         </is>
       </c>
     </row>
@@ -31197,7 +31197,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Có lẽ Quả Cầu Sonoro quyết định ai có thể nhìn thấy và ai không.</t>
+          <t>Có lẽ Sonoro Sphere quyết định ai có thể nhìn thấy và ai không.</t>
         </is>
       </c>
     </row>
@@ -32432,7 +32432,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Ừ hử. Được rồi. Ta hiểu rồi...</t>
+          <t>Ừ hử. Được rồi. Tao hiểu rồi...</t>
         </is>
       </c>
     </row>
@@ -32822,7 +32822,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Ôi. Cậu thật tốt bụng quá.</t>
+          <t>Ôi. bạn thật tốt bụng quá.</t>
         </is>
       </c>
     </row>
